--- a/backend_for_testcase/src/test/resources/test-data/excel.xlsx
+++ b/backend_for_testcase/src/test/resources/test-data/excel.xlsx
@@ -7,11 +7,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Mdm4OrNwOp/2G0kuxkJ2nNResON3tFmKcvbDp15EfTg="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -55,51 +60,37 @@
     <t>정상 로그인 완료</t>
   </si>
   <si>
-    <t>00 API 테스트</t>
+    <t>01 로그아웃 기능 테스트</t>
+  </si>
+  <si>
+    <t>사용자 로그아웃 검증</t>
+  </si>
+  <si>
+    <t>로그인 상태</t>
+  </si>
+  <si>
+    <t>[{"stepNumber":1,"description":"로그아웃 버튼 클릭","expectedResult":"로그아웃 성공"}]</t>
+  </si>
+  <si>
+    <t>정상 로그아웃 완료</t>
+  </si>
+  <si>
+    <t>로그인/로그아웃 폴더</t>
   </si>
   <si>
     <t>folder</t>
-  </si>
-  <si>
-    <t>API 관련 테스트</t>
-  </si>
-  <si>
-    <t>00 결제 기능 테스트</t>
-  </si>
-  <si>
-    <t>결제 플로우 검증
-122344
-1111
-1111
-1111</t>
-  </si>
-  <si>
-    <t>계정 등록 필요</t>
-  </si>
-  <si>
-    <t>[{"stepNumber":1,"description":"결제 수단 선택","expectedResult":"결제창 표시"}]</t>
-  </si>
-  <si>
-    <t>결제 완료 상태 확인</t>
-  </si>
-  <si>
-    <t>API 테스트</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -139,23 +130,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -367,106 +352,106 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="15.75"/>
+    <col customWidth="1" min="2" max="2" width="12.63"/>
     <col customWidth="1" min="3" max="3" width="13.5"/>
     <col customWidth="1" min="4" max="4" width="11.25"/>
     <col customWidth="1" min="5" max="5" width="59.5"/>
     <col customWidth="1" min="6" max="6" width="13.88"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4">
+      <c r="G2" s="3"/>
+      <c r="H2" s="2">
         <v>1.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4">
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2">
         <v>2.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1.0</v>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2">
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
